--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121683663</v>
+        <v>121683714</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121683495</v>
+        <v>121690085</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -945,17 +945,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Fålamyran, Fålamyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627980</v>
+        <v>627868</v>
       </c>
       <c r="R4" t="n">
-        <v>6896860</v>
+        <v>6897007</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121690085</v>
+        <v>121683663</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,41 +1033,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fålamyran, Fålamyran, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627868</v>
+        <v>627970</v>
       </c>
       <c r="R5" t="n">
-        <v>6897007</v>
+        <v>6896913</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121683456</v>
+        <v>121683596</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,49 +1145,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627993</v>
+        <v>627972</v>
       </c>
       <c r="R6" t="n">
-        <v>6896823</v>
+        <v>6896918</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121685013</v>
+        <v>121683495</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,43 +1257,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627866</v>
+        <v>627980</v>
       </c>
       <c r="R7" t="n">
-        <v>6896945</v>
+        <v>6896860</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121683714</v>
+        <v>121683456</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,41 +1369,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627970</v>
+        <v>627993</v>
       </c>
       <c r="R8" t="n">
-        <v>6896913</v>
+        <v>6896823</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121683596</v>
+        <v>121685013</v>
       </c>
       <c r="B10" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,38 +1621,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627972</v>
+        <v>627866</v>
       </c>
       <c r="R10" t="n">
-        <v>6896918</v>
+        <v>6896945</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121683714</v>
+        <v>121683663</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121690085</v>
+        <v>121683714</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fålamyran, Fålamyran, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627868</v>
+        <v>627970</v>
       </c>
       <c r="R4" t="n">
-        <v>6897007</v>
+        <v>6896913</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121683663</v>
+        <v>121683058</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>90778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627970</v>
+        <v>628023</v>
       </c>
       <c r="R5" t="n">
-        <v>6896913</v>
+        <v>6896812</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,6 +1117,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1133,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121683596</v>
+        <v>121690085</v>
       </c>
       <c r="B6" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,41 +1165,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Fålamyran, Fålamyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627972</v>
+        <v>627868</v>
       </c>
       <c r="R6" t="n">
-        <v>6896918</v>
+        <v>6897007</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121683495</v>
+        <v>121683596</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1277,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627980</v>
+        <v>627972</v>
       </c>
       <c r="R7" t="n">
-        <v>6896860</v>
+        <v>6896918</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121683456</v>
+        <v>121685013</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1391,27 +1411,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627993</v>
+        <v>627866</v>
       </c>
       <c r="R8" t="n">
-        <v>6896823</v>
+        <v>6896945</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121683058</v>
+        <v>121683456</v>
       </c>
       <c r="B9" t="n">
-        <v>90778</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,41 +1506,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5321</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628023</v>
+        <v>627993</v>
       </c>
       <c r="R9" t="n">
-        <v>6896812</v>
+        <v>6896823</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,26 +1598,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1609,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121685013</v>
+        <v>121683495</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,43 +1626,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627866</v>
+        <v>627980</v>
       </c>
       <c r="R10" t="n">
-        <v>6896945</v>
+        <v>6896860</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121686793</v>
       </c>
       <c r="B2" t="n">
-        <v>57369</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121683456</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>121685013</v>
       </c>
       <c r="B7" t="n">
-        <v>57369</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121686793</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121683456</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>121685013</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121686793</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121683456</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>121685013</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121686793</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121683456</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>121685013</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121686793</v>
+        <v>121683058</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åboberget, Åboberget, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627840</v>
+        <v>628023</v>
       </c>
       <c r="R2" t="n">
-        <v>6896970</v>
+        <v>6896812</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två uthackade bohål i död, exponerad tallved (ca 4-5m höjd).</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,61 +802,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121683456</v>
+        <v>121683596</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627993</v>
+        <v>627972</v>
       </c>
       <c r="R3" t="n">
-        <v>6896823</v>
+        <v>6896918</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121683663</v>
+        <v>121681249</v>
       </c>
       <c r="B4" t="n">
-        <v>90772</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627970</v>
+        <v>628068</v>
       </c>
       <c r="R4" t="n">
-        <v>6896913</v>
+        <v>6896792</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tall med många ringhack, svårt att bedöma ålder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,53 +1026,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121683058</v>
+        <v>121683456</v>
       </c>
       <c r="B5" t="n">
-        <v>90804</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628023</v>
+        <v>627993</v>
       </c>
       <c r="R5" t="n">
-        <v>6896812</v>
+        <v>6896823</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,26 +1125,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1161,50 +1141,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121683495</v>
+        <v>121685013</v>
       </c>
       <c r="B6" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627980</v>
+        <v>627866</v>
       </c>
       <c r="R6" t="n">
-        <v>6896860</v>
+        <v>6896945</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,15 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121685013</v>
+        <v>121686793</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,19 +1284,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Åboberget, Åboberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627866</v>
+        <v>627840</v>
       </c>
       <c r="R7" t="n">
-        <v>6896945</v>
+        <v>6896970</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Två uthackade bohål i död, exponerad tallved (ca 4-5m höjd).</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,53 +1370,58 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121690085</v>
+        <v>133654704</v>
       </c>
       <c r="B8" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fålamyran, Fålamyran, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627868</v>
+        <v>628100</v>
       </c>
       <c r="R8" t="n">
-        <v>6897007</v>
+        <v>6896829</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,22 +1445,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,27 +1465,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121683596</v>
+        <v>121683714</v>
       </c>
       <c r="B9" t="n">
-        <v>90719</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627972</v>
+        <v>627970</v>
       </c>
       <c r="R9" t="n">
-        <v>6896918</v>
+        <v>6896913</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1577,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,37 +1584,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121683714</v>
+        <v>121683495</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1654,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627970</v>
+        <v>627980</v>
       </c>
       <c r="R10" t="n">
-        <v>6896913</v>
+        <v>6896860</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,6 +1688,113 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121690085</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fålamyran, Fålamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>627868</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6897007</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55548-2024 artfynd.xlsx
+++ b/artfynd/A 55548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121683596</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121685013</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121686793</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121683714</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121683495</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121690085</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121683058</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681249</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121683456</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1795,8 +1845,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133654704</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>